--- a/Methane/Methane_Bio_Brownfield_Höchst/Datenbank.xlsx
+++ b/Methane/Methane_Bio_Brownfield_Höchst/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_Bio_Brownfield_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_Brownfield_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75053093-AF31-48FA-8C4F-F9D0D529B0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E81AA1E-B5C7-427A-9FF7-8AF4D4398F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -40,11 +40,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={AFE4F70E-4F68-4601-B8CF-DFA896FC8A62}</author>
-    <author>tc={A66B6FDD-7E3A-402B-8E6B-7073C79B9436}</author>
-    <author>tc={5F7F21A6-9267-43AB-9E2F-857C43A6B051}</author>
-    <author>tc={87F94307-F9C1-413A-A184-19A69689A8AF}</author>
-    <author>tc={011C4874-472E-423F-9F9E-1A44747EBF50}</author>
-    <author>tc={F7866A31-18E0-48C6-B567-67C836D4C8B7}</author>
     <author>Timon Geiß</author>
   </authors>
   <commentList>
@@ -56,53 +51,7 @@
     Gleiches wie Ammonia?</t>
       </text>
     </comment>
-    <comment ref="E18" authorId="1" shapeId="0" xr:uid="{A66B6FDD-7E3A-402B-8E6B-7073C79B9436}">
-      <text>
-        <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    0,7 * 10^6 /1000 </t>
-      </text>
-    </comment>
-    <comment ref="E23" authorId="2" shapeId="0" xr:uid="{5F7F21A6-9267-43AB-9E2F-857C43A6B051}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    1750 kWh_th/t durch 1000</t>
-      </text>
-    </comment>
-    <comment ref="E24" authorId="3" shapeId="0" xr:uid="{87F94307-F9C1-413A-A184-19A69689A8AF}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    800 €/t*a * 8760 h/a / 1000 kg/t = €/kg *h</t>
-      </text>
-    </comment>
-    <comment ref="E25" authorId="4" shapeId="0" xr:uid="{011C4874-472E-423F-9F9E-1A44747EBF50}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    ~ 40 opex/ 800 capex</t>
-      </text>
-    </comment>
-    <comment ref="E39" authorId="5" shapeId="0" xr:uid="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    Wochenfaktor 4,33 * 24h *7d = 727,44h/monat
-4,55 %/monat * 1/727,44 monat/h
-Antwort:
-    Wochenfaktor 4,33 * 24h * 7d= 727,44 h/monat
-4,55 %/monat * 1/727 monat/h
-Antwort:
-    55 % pro Monat --&gt; /31 = 1,77 %/d --&gt; / 24 = 0,074 %/h</t>
-      </text>
-    </comment>
-    <comment ref="E49" authorId="6" shapeId="0" xr:uid="{22946658-3822-4C9A-8007-CC034FA9B8AB}">
+    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{22946658-3822-4C9A-8007-CC034FA9B8AB}">
       <text>
         <r>
           <rPr>
@@ -126,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E50" authorId="6" shapeId="0" xr:uid="{426A9046-86EB-4AF9-8A2D-1FEFC7B6C4A3}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{426A9046-86EB-4AF9-8A2D-1FEFC7B6C4A3}">
       <text>
         <r>
           <rPr>
@@ -150,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="6" shapeId="0" xr:uid="{360FC6EE-8AD3-4EF7-B2BF-00DD1029DCAF}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{360FC6EE-8AD3-4EF7-B2BF-00DD1029DCAF}">
       <text>
         <r>
           <rPr>
@@ -179,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="286">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -741,9 +690,6 @@
     <t>result_bat_leistung</t>
   </si>
   <si>
-    <t>kW_el</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -870,30 +816,6 @@
     <t>Schattenvariable Einnahmen Stromverkauf</t>
   </si>
   <si>
-    <t>CO2-Bereitstellung / Direct Air Capture</t>
-  </si>
-  <si>
-    <t>strombedarf_dac</t>
-  </si>
-  <si>
-    <t>capex_dac</t>
-  </si>
-  <si>
-    <t>opex_dac</t>
-  </si>
-  <si>
-    <t>lebensdauer_dac</t>
-  </si>
-  <si>
-    <t>zinssatz_dac</t>
-  </si>
-  <si>
-    <t>kWh/kg_CO2</t>
-  </si>
-  <si>
-    <t>€/kg_CO2 *h</t>
-  </si>
-  <si>
     <t>Kohlenstoffdioxidbedarf Mengenverhältnis</t>
   </si>
   <si>
@@ -906,33 +828,6 @@
     <t>kg_CO2/a</t>
   </si>
   <si>
-    <t>annuity_dac</t>
-  </si>
-  <si>
-    <t>result_dac_leistung</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_elin</t>
-  </si>
-  <si>
-    <t>calc_gesamtinvest_dac</t>
-  </si>
-  <si>
-    <t>calc_opex_fix_dac</t>
-  </si>
-  <si>
-    <t>calc_annuity_dac</t>
-  </si>
-  <si>
-    <t>calc_verzinstinvest_dac</t>
-  </si>
-  <si>
-    <t>calc_cost_dac</t>
-  </si>
-  <si>
-    <t>Kohlendioxidproduktion</t>
-  </si>
-  <si>
     <t>Gesamtkosten pro kg Kohlendioxid</t>
   </si>
   <si>
@@ -942,210 +837,9 @@
     <t>Gesamtkosten pro t Methanol</t>
   </si>
   <si>
-    <t>Heatpump</t>
-  </si>
-  <si>
-    <t>eta_hp</t>
-  </si>
-  <si>
-    <t>strombedarf_hp</t>
-  </si>
-  <si>
-    <t>capex_hp</t>
-  </si>
-  <si>
-    <t>opex_hp</t>
-  </si>
-  <si>
-    <t>lebensdauer_hp</t>
-  </si>
-  <si>
-    <t>zinssatz_hp</t>
-  </si>
-  <si>
-    <t>€/kW_th</t>
-  </si>
-  <si>
-    <t>Wärmebedarf</t>
-  </si>
-  <si>
-    <t>waerme_bedarf_dac</t>
-  </si>
-  <si>
-    <t>kWh_th/kg_CO2</t>
-  </si>
-  <si>
-    <t>annuity_hp</t>
-  </si>
-  <si>
-    <t>result_hp_leistung</t>
-  </si>
-  <si>
-    <t>result_hp_flowsum_elin</t>
-  </si>
-  <si>
-    <t>calc_gesamtinvest_hp</t>
-  </si>
-  <si>
-    <t>calc_opex_fix_hp</t>
-  </si>
-  <si>
-    <t>calc_annuity_hp</t>
-  </si>
-  <si>
-    <t>calc_verzinstinvest_hp</t>
-  </si>
-  <si>
-    <t>calc_cost_hp</t>
-  </si>
-  <si>
-    <t>€/ kW_th a</t>
-  </si>
-  <si>
-    <t>MWh_th/a</t>
-  </si>
-  <si>
-    <t>Waermeproduktion</t>
-  </si>
-  <si>
-    <t>result_hp_flowsum_qout</t>
-  </si>
-  <si>
-    <t>MWh_el/a</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_co2out</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_qin</t>
-  </si>
-  <si>
-    <t>Wärme Verkauf</t>
-  </si>
-  <si>
-    <t>Waerme Verkaufspreis</t>
-  </si>
-  <si>
-    <t>waermeerloes</t>
-  </si>
-  <si>
-    <t>kW_el/kW_th</t>
-  </si>
-  <si>
-    <t>Waerme Verkauf</t>
-  </si>
-  <si>
-    <t>Waermeverkauf</t>
-  </si>
-  <si>
-    <t>result_qverkauf_flowsum</t>
-  </si>
-  <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
-  </si>
-  <si>
-    <t>Einnahmen aus Wärmeverkauf</t>
-  </si>
-  <si>
     <t>calc_annuity_gesamt</t>
   </si>
   <si>
-    <t>Levelized Cost of Heatpump</t>
-  </si>
-  <si>
-    <t>calc_lcoh_hp</t>
-  </si>
-  <si>
-    <t>Gesamtkosten pro kWh thermisch</t>
-  </si>
-  <si>
-    <t>calc_cost_q</t>
-  </si>
-  <si>
-    <t>ct/kWh_th</t>
-  </si>
-  <si>
-    <t>Wärmespeicher</t>
-  </si>
-  <si>
-    <t>capex_qs</t>
-  </si>
-  <si>
-    <t>opex_qs</t>
-  </si>
-  <si>
-    <t>lebensdauer_qs</t>
-  </si>
-  <si>
-    <t>verlustrate_qs</t>
-  </si>
-  <si>
-    <t>eta_einspeichern_qs</t>
-  </si>
-  <si>
-    <t>eta_ausspeichern_qs</t>
-  </si>
-  <si>
-    <t>zinssatz_qs</t>
-  </si>
-  <si>
-    <t>fuellstand_qs</t>
-  </si>
-  <si>
-    <t>€/kWh_th</t>
-  </si>
-  <si>
-    <t>annuity_qs</t>
-  </si>
-  <si>
-    <t>result_qs_kapa</t>
-  </si>
-  <si>
-    <t>result_qs_flowsum_in</t>
-  </si>
-  <si>
-    <t>result_qs_flowsum_out</t>
-  </si>
-  <si>
-    <t>calc_gesamtinvest_qs</t>
-  </si>
-  <si>
-    <t>calc_opex_fix_qs</t>
-  </si>
-  <si>
-    <t>calc_annuity_qs</t>
-  </si>
-  <si>
-    <t>calc_verzinstinvest_qs</t>
-  </si>
-  <si>
-    <t>calc_cost_qs</t>
-  </si>
-  <si>
-    <t>Levelized Cost of Heatstorage</t>
-  </si>
-  <si>
-    <t>calc_lcoh_qs</t>
-  </si>
-  <si>
-    <t>Levelized Cost of Heat</t>
-  </si>
-  <si>
-    <t>calc_lcoh_q</t>
-  </si>
-  <si>
-    <t>€/ kWh_th a</t>
-  </si>
-  <si>
-    <t>kWh_th</t>
-  </si>
-  <si>
     <t>Verkaufspreiseanalyse</t>
   </si>
   <si>
@@ -1159,9 +853,6 @@
   </si>
   <si>
     <t>calc_price</t>
-  </si>
-  <si>
-    <t>kWh_th/a</t>
   </si>
   <si>
     <t>€/ kg a</t>
@@ -1304,10 +995,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1439,47 +1130,45 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1487,6 +1176,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1519,10 +1211,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1544,7 +1236,6 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Timon Geiß" id="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" userId="73709f7862571f8c" providerId="Windows Live"/>
-  <person displayName="Michael Heberl" id="{1C9DF23A-CC4A-4BFD-AF20-2D2787398686}" userId="S::hem38994@hs-regensburg.de::dfa4a7cd-e6f0-4c5c-8753-628b8838436a" providerId="AD"/>
 </personList>
 </file>
 
@@ -1814,39 +1505,16 @@
   <threadedComment ref="E9" dT="2025-03-14T08:21:08.14" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{AFE4F70E-4F68-4601-B8CF-DFA896FC8A62}">
     <text>Gleiches wie Ammonia?</text>
   </threadedComment>
-  <threadedComment ref="E18" dT="2025-03-18T08:08:24.46" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{A66B6FDD-7E3A-402B-8E6B-7073C79B9436}">
-    <text xml:space="preserve">0,7 * 10^6 /1000 </text>
-  </threadedComment>
-  <threadedComment ref="E23" dT="2025-03-18T08:05:52.08" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{5F7F21A6-9267-43AB-9E2F-857C43A6B051}">
-    <text>1750 kWh_th/t durch 1000</text>
-  </threadedComment>
-  <threadedComment ref="E24" dT="2025-03-14T09:24:29.74" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{87F94307-F9C1-413A-A184-19A69689A8AF}">
-    <text>800 €/t*a * 8760 h/a / 1000 kg/t = €/kg *h</text>
-  </threadedComment>
-  <threadedComment ref="E25" dT="2025-03-14T09:25:24.78" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{011C4874-472E-423F-9F9E-1A44747EBF50}">
-    <text>~ 40 opex/ 800 capex</text>
-  </threadedComment>
-  <threadedComment ref="E39" dT="2025-03-26T10:22:08.04" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
-    <text>Wochenfaktor 4,33 * 24h *7d = 727,44h/monat
-4,55 %/monat * 1/727,44 monat/h</text>
-  </threadedComment>
-  <threadedComment ref="E39" dT="2025-03-26T10:28:05.27" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{02E78AB9-E14B-4034-A3AB-3EF5F06F95CB}" parentId="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
-    <text>Wochenfaktor 4,33 * 24h * 7d= 727,44 h/monat
-4,55 %/monat * 1/727 monat/h</text>
-  </threadedComment>
-  <threadedComment ref="E39" dT="2025-04-02T11:01:30.13" personId="{1C9DF23A-CC4A-4BFD-AF20-2D2787398686}" id="{7A1231DE-7CE0-49C4-BF40-EE9EE75E0E1A}" parentId="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
-    <text>55 % pro Monat --&gt; /31 = 1,77 %/d --&gt; / 24 = 0,074 %/h</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="22" customWidth="1"/>
     <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
@@ -1878,13 +1546,13 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="23"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1902,7 +1570,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
-      <c r="B3" s="40"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -1918,7 +1586,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
-      <c r="B4" s="40"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1934,7 +1602,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="33"/>
-      <c r="B5" s="40"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1950,7 +1618,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="33"/>
-      <c r="B6" s="40"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1966,7 +1634,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="33"/>
-      <c r="B7" s="40"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1982,31 +1650,31 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="33"/>
-      <c r="B8" s="43" t="s">
-        <v>329</v>
+      <c r="B8" s="44" t="s">
+        <v>243</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="E8" s="14">
         <f>0.36</f>
         <v>0.36</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>338</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="33"/>
-      <c r="B9" s="40"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>331</v>
+        <v>245</v>
       </c>
       <c r="E9" s="9">
         <v>285.39999999999998</v>
@@ -2017,28 +1685,28 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="33"/>
-      <c r="B10" s="40"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="E10" s="9">
         <v>7700</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>339</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="33"/>
-      <c r="B11" s="40"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>333</v>
+        <v>247</v>
       </c>
       <c r="E11" s="11">
         <v>0.05</v>
@@ -2049,44 +1717,44 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="33"/>
-      <c r="B12" s="40"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>334</v>
+        <v>248</v>
       </c>
       <c r="E12" s="9">
         <v>0.46</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>340</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="33"/>
-      <c r="B13" s="40"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>335</v>
+        <v>249</v>
       </c>
       <c r="E13" s="9">
         <v>2.54</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>341</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="33"/>
-      <c r="B14" s="40"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>336</v>
+        <v>250</v>
       </c>
       <c r="E14" s="12">
         <v>20</v>
@@ -2095,14 +1763,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="33"/>
-      <c r="B15" s="44"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>337</v>
+        <v>251</v>
       </c>
       <c r="E15" s="16">
         <v>0.06</v>
@@ -2112,509 +1780,513 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E16" s="17">
-        <v>3.7</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>22</v>
+      <c r="A16" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="18">
+        <v>490</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="6" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>255</v>
+        <v>40</v>
       </c>
       <c r="E17" s="11">
-        <v>0.27</v>
+        <v>0.01</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>282</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
+      <c r="B18" s="37"/>
       <c r="C18" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E18" s="11">
-        <v>700</v>
+        <v>32</v>
+      </c>
+      <c r="E18" s="12">
+        <v>20</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>260</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="6" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="E19" s="11">
-        <v>0.02</v>
+        <v>34</v>
+      </c>
+      <c r="E19" s="23">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
+      <c r="B20" s="37"/>
       <c r="C20" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>258</v>
+        <v>37</v>
       </c>
       <c r="E20" s="11">
-        <v>20</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="33"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="F21" s="15" t="s">
+      <c r="B21" s="37"/>
+      <c r="C21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="33"/>
-      <c r="B22" s="36" t="s">
-        <v>229</v>
-      </c>
+      <c r="B22" s="37"/>
       <c r="C22" s="6" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.5</v>
+        <v>31</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0.05</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="33"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1.75</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>263</v>
+      <c r="B23" s="38"/>
+      <c r="C23" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="16">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E24" s="9">
-        <v>7000</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>236</v>
+      <c r="B24" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="17">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="33"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E25" s="11">
-        <v>0.05</v>
+        <v>55</v>
+      </c>
+      <c r="E25" s="9">
+        <f>E26*4</f>
+        <v>424</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="33"/>
-      <c r="B26" s="36"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" s="12">
-        <v>15</v>
+        <v>56</v>
+      </c>
+      <c r="E26" s="9">
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
-      <c r="B27" s="36"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="E27" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F27" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="33"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="18">
-        <v>490</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="33"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="6" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E29" s="11">
-        <v>0.01</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="33"/>
-      <c r="B30" s="36"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="6" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="12">
-        <v>20</v>
+        <v>58</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.25</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="33"/>
-      <c r="B31" s="36"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="6" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="24">
-        <v>1.0000000000000001E-5</v>
+        <v>61</v>
+      </c>
+      <c r="E31" s="11">
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="33"/>
-      <c r="B32" s="36"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="11">
-        <v>0.83299999999999996</v>
+        <v>54</v>
+      </c>
+      <c r="E32" s="12">
+        <v>15</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="34"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="11">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="11">
-        <v>0.05</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="33"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="16">
+      <c r="A34" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="47">
+        <v>0.1699</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="35"/>
+      <c r="B35" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E35" s="11">
         <v>0</v>
       </c>
-      <c r="F35" s="15" t="s">
-        <v>94</v>
+      <c r="F35" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="33"/>
-      <c r="B36" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E36" s="18">
-        <v>2.83</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>305</v>
+      <c r="B36" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="17">
+        <v>0.99</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="33"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E37" s="11">
-        <v>0.03</v>
+        <v>43</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1100</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="33"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="E38" s="12">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="E38" s="1">
+        <v>17.84</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="33"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E39" s="11">
-        <v>7.3999999999999999E-4</v>
+        <v>45</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="33"/>
-      <c r="B40" s="36"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E40" s="11">
-        <v>0.98</v>
+        <v>42</v>
+      </c>
+      <c r="E40" s="12">
+        <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="33"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="6" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E41" s="11">
-        <v>0.98</v>
+        <v>67</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1000000</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="33"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="38"/>
+      <c r="C42" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E42" s="11">
-        <v>0.05</v>
-      </c>
-      <c r="F42" s="6" t="s">
+      <c r="D42" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="16">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F42" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="E43" s="16">
-        <v>0</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>94</v>
+      <c r="B43" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="17">
+        <v>0.997</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="33"/>
-      <c r="B44" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="17">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>95</v>
+      <c r="B44" s="37"/>
+      <c r="C44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1080</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="33"/>
-      <c r="B45" s="40"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="9">
-        <f>E46*4</f>
-        <v>424</v>
+        <v>52</v>
+      </c>
+      <c r="E45" s="1">
+        <v>12.68</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="33"/>
-      <c r="B46" s="40"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" s="9">
-        <v>106</v>
+        <v>49</v>
+      </c>
+      <c r="E46" s="2">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>19</v>
@@ -2622,471 +2294,120 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="33"/>
-      <c r="B47" s="40"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>50</v>
+      </c>
+      <c r="E47" s="12">
+        <v>25</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="33"/>
-      <c r="B48" s="40"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="6" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E48" s="11">
-        <v>0.93500000000000005</v>
+        <v>65</v>
+      </c>
+      <c r="E48" s="21">
+        <v>1000000</v>
       </c>
       <c r="F48" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="34"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="20">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="F49" s="19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="11">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>90</v>
+      <c r="A50" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" s="26">
+        <v>-1E-4</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="33"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="11">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>94</v>
+      <c r="B51" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="29">
+        <v>-1.5</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="12">
-        <v>15</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="34"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="18">
-        <v>0.1699</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="45"/>
-      <c r="B55" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E55" s="11">
-        <v>0</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56" s="17">
-        <v>0.99</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1100</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" s="1">
-        <v>17.84</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="9">
-        <v>0</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E60" s="12">
-        <v>25</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E61" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="37"/>
-      <c r="C62" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E62" s="16">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E63" s="17">
-        <v>0.997</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1080</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E65" s="1">
-        <v>12.68</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" s="12">
-        <v>25</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E68" s="21">
-        <v>1000000</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="34"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="20">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D70" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="27">
-        <v>-1E-4</v>
-      </c>
-      <c r="F70" s="26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
-      <c r="B71" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E71" s="11">
-        <v>-1E-4</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33"/>
-      <c r="B72" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D72" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72" s="30">
-        <v>-1.5</v>
-      </c>
-      <c r="F72" s="29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="34"/>
-      <c r="B73" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="E73" s="20">
+      <c r="A52" s="34"/>
+      <c r="B52" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E52" s="20">
         <v>-1.7</v>
       </c>
-      <c r="F73" s="19" t="s">
-        <v>339</v>
+      <c r="F52" s="19" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A2:A27"/>
-    <mergeCell ref="A28:A53"/>
-    <mergeCell ref="A54:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="B63:B69"/>
-    <mergeCell ref="B44:B53"/>
+  <mergeCells count="10">
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A16:A33"/>
+    <mergeCell ref="A34:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="B36:B42"/>
+    <mergeCell ref="B43:B49"/>
+    <mergeCell ref="B24:B33"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="B8:B15"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B36:B43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3096,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
@@ -3132,7 +2453,7 @@
       <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -3148,7 +2469,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
-      <c r="B3" s="40"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="6" t="s">
         <v>107</v>
       </c>
@@ -3162,7 +2483,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
-      <c r="B4" s="40"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
@@ -3176,7 +2497,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="33"/>
-      <c r="B5" s="40"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="6" t="s">
         <v>138</v>
       </c>
@@ -3190,7 +2511,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="33"/>
-      <c r="B6" s="40"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
@@ -3204,7 +2525,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="33"/>
-      <c r="B7" s="40"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
         <v>155</v>
       </c>
@@ -3218,12 +2539,12 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="33"/>
-      <c r="B8" s="40"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="6" t="s">
@@ -3232,7 +2553,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="33"/>
-      <c r="B9" s="40"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
@@ -3246,12 +2567,12 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="33"/>
-      <c r="B10" s="40"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="6" t="s">
@@ -3260,19 +2581,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="33"/>
-      <c r="B11" s="40"/>
+      <c r="B11" s="41"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="33"/>
-      <c r="B12" s="43" t="s">
-        <v>329</v>
+      <c r="B12" s="44" t="s">
+        <v>243</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>342</v>
+        <v>256</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="13" t="s">
@@ -3281,26 +2602,26 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="33"/>
-      <c r="B13" s="40"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="6" t="s">
-        <v>353</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="33"/>
-      <c r="B14" s="40"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>343</v>
+        <v>257</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
@@ -3309,26 +2630,26 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="33"/>
-      <c r="B15" s="40"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="6" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="6" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="33"/>
-      <c r="B16" s="40"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="6" t="s">
@@ -3337,12 +2658,12 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>346</v>
+        <v>260</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="6" t="s">
@@ -3351,12 +2672,12 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="6" t="s">
         <v>155</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>347</v>
+        <v>261</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="6" t="s">
@@ -3365,12 +2686,12 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="6" t="s">
@@ -3379,12 +2700,12 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="6" t="s">
         <v>167</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>349</v>
+        <v>263</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="6" t="s">
@@ -3393,134 +2714,136 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="33"/>
-      <c r="B21" s="40"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>350</v>
+        <v>264</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="33"/>
-      <c r="B22" s="44"/>
+      <c r="B22" s="45"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="6" t="s">
-        <v>272</v>
+    <row r="23" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="7" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
-      <c r="B24" s="40"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E24" s="9"/>
+        <v>110</v>
+      </c>
+      <c r="E24" s="11"/>
       <c r="F24" s="6" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="33"/>
-      <c r="B25" s="40"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="6" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E25" s="11"/>
+        <v>133</v>
+      </c>
+      <c r="E25" s="12"/>
       <c r="F25" s="6" t="s">
-        <v>276</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="33"/>
-      <c r="B26" s="40"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="6" t="s">
-        <v>274</v>
+        <v>136</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E26" s="12"/>
+        <v>134</v>
+      </c>
+      <c r="E26" s="11"/>
       <c r="F26" s="6" t="s">
-        <v>273</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
-      <c r="B27" s="40"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E27" s="12"/>
+        <v>146</v>
+      </c>
+      <c r="E27" s="11"/>
       <c r="F27" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="33"/>
-      <c r="B28" s="40"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="6" t="s">
         <v>155</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E28" s="12"/>
+        <v>159</v>
+      </c>
+      <c r="E28" s="11"/>
       <c r="F28" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="33"/>
-      <c r="B29" s="40"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E29" s="12"/>
+        <v>198</v>
+      </c>
+      <c r="E29" s="11"/>
       <c r="F29" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="33"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="37"/>
       <c r="C30" s="6" t="s">
         <v>167</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>270</v>
+        <v>171</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="6" t="s">
@@ -3529,12 +2852,12 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="33"/>
-      <c r="B31" s="40"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>271</v>
+        <v>192</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="6" t="s">
@@ -3543,7 +2866,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="33"/>
-      <c r="B32" s="44"/>
+      <c r="B32" s="38"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
@@ -3551,355 +2874,351 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="33"/>
-      <c r="B33" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="C33" s="6" t="s">
+      <c r="B33" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="6" t="s">
-        <v>104</v>
+      <c r="D33" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="E34" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="E34" s="11"/>
       <c r="F34" s="6" t="s">
-        <v>186</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="33"/>
-      <c r="B35" s="36"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="6" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E35" s="11"/>
+        <v>112</v>
+      </c>
+      <c r="E35" s="9"/>
       <c r="F35" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="33"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="6" t="s">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E36" s="11"/>
+        <v>185</v>
+      </c>
+      <c r="E36" s="9"/>
       <c r="F36" s="6" t="s">
-        <v>273</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="33"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="6" t="s">
-        <v>249</v>
+        <v>126</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E37" s="12"/>
+        <v>124</v>
+      </c>
+      <c r="E37" s="9"/>
       <c r="F37" s="6" t="s">
-        <v>240</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="33"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="12"/>
+        <v>125</v>
+      </c>
+      <c r="E38" s="11"/>
       <c r="F38" s="6" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="33"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="41"/>
       <c r="C39" s="6" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="12"/>
+        <v>145</v>
+      </c>
+      <c r="E39" s="9"/>
       <c r="F39" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="33"/>
-      <c r="B40" s="36"/>
+      <c r="B40" s="41"/>
       <c r="C40" s="6" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E40" s="12"/>
+        <v>157</v>
+      </c>
+      <c r="E40" s="11"/>
       <c r="F40" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="33"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="6" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="33"/>
-      <c r="B42" s="36"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="6" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>248</v>
+        <v>170</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="33"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E43" s="11"/>
+      <c r="F43" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="33"/>
-      <c r="B43" s="36"/>
-      <c r="E43" s="11"/>
-    </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="7" t="s">
-        <v>327</v>
-      </c>
+    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="34"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="19"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="6" t="s">
-        <v>328</v>
+      <c r="A45" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="18"/>
+      <c r="F45" s="7" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="33"/>
-      <c r="B46" s="36"/>
+      <c r="B46" s="41"/>
       <c r="C46" s="6" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" s="12"/>
+        <v>152</v>
+      </c>
+      <c r="E46" s="9"/>
       <c r="F46" s="6" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="33"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="15"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="33"/>
-      <c r="B48" s="36"/>
+      <c r="B48" s="41" t="s">
+        <v>279</v>
+      </c>
       <c r="C48" s="6" t="s">
-        <v>141</v>
+        <v>282</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E48" s="11"/>
+        <v>283</v>
+      </c>
+      <c r="E48" s="9"/>
       <c r="F48" s="6" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="33"/>
-      <c r="B49" s="36"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="6" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E49" s="11"/>
+        <v>285</v>
+      </c>
+      <c r="E49" s="9"/>
       <c r="F49" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="33"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B50" s="41"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="33"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="6" t="s">
-        <v>140</v>
+      <c r="B51" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51" s="17"/>
+      <c r="F51" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="33"/>
-      <c r="B52" s="36"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="6" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E52" s="11"/>
+        <v>109</v>
+      </c>
+      <c r="E52" s="1"/>
       <c r="F52" s="6" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="33"/>
       <c r="B53" s="37"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="15"/>
+      <c r="C53" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="33"/>
-      <c r="B54" s="36" t="s">
-        <v>296</v>
-      </c>
+      <c r="B54" s="37"/>
       <c r="C54" s="6" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>306</v>
+        <v>144</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="6" t="s">
-        <v>319</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="33"/>
-      <c r="B55" s="36"/>
+      <c r="B55" s="37"/>
       <c r="C55" s="6" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E55" s="11"/>
+        <v>156</v>
+      </c>
+      <c r="E55" s="12"/>
       <c r="F55" s="6" t="s">
-        <v>320</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="33"/>
-      <c r="B56" s="36"/>
+      <c r="B56" s="37"/>
       <c r="C56" s="6" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E56" s="12"/>
+        <v>162</v>
+      </c>
+      <c r="E56" s="9"/>
       <c r="F56" s="6" t="s">
-        <v>326</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="33"/>
-      <c r="B57" s="36"/>
+      <c r="B57" s="37"/>
       <c r="C57" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E57" s="11"/>
+        <v>197</v>
+      </c>
+      <c r="E57" s="9"/>
       <c r="F57" s="6" t="s">
-        <v>326</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
+      <c r="B58" s="37"/>
       <c r="C58" s="6" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>310</v>
+        <v>169</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="6" t="s">
@@ -3908,12 +3227,12 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
+      <c r="B59" s="37"/>
       <c r="C59" s="6" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="6" t="s">
@@ -3922,173 +3241,166 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E60" s="11"/>
-      <c r="F60" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B60" s="38"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="33"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="E61" s="11"/>
-      <c r="F61" s="6" t="s">
-        <v>140</v>
+      <c r="B61" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="17"/>
+      <c r="F61" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="33"/>
-      <c r="B62" s="36"/>
+      <c r="B62" s="37"/>
       <c r="C62" s="6" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E62" s="11"/>
+        <v>106</v>
+      </c>
+      <c r="E62" s="1"/>
       <c r="F62" s="6" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="33"/>
       <c r="B63" s="37"/>
-      <c r="E63" s="11"/>
+      <c r="C63" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" s="1"/>
+      <c r="F63" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="33"/>
-      <c r="B64" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E64" s="17"/>
-      <c r="F64" s="13" t="s">
-        <v>98</v>
+      <c r="B64" s="37"/>
+      <c r="C64" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
+      <c r="B65" s="37"/>
       <c r="C65" s="6" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E65" s="11"/>
+        <v>154</v>
+      </c>
+      <c r="E65" s="12"/>
       <c r="F65" s="6" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="33"/>
-      <c r="B66" s="40"/>
+      <c r="B66" s="37"/>
       <c r="C66" s="6" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E66" s="9"/>
+        <v>160</v>
+      </c>
+      <c r="E66" s="21"/>
       <c r="F66" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="33"/>
-      <c r="B67" s="40"/>
+      <c r="B67" s="37"/>
       <c r="C67" s="6" t="s">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E67" s="9"/>
+        <v>196</v>
+      </c>
+      <c r="E67" s="21"/>
       <c r="F67" s="6" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="33"/>
-      <c r="B68" s="40"/>
+      <c r="B68" s="37"/>
       <c r="C68" s="6" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E68" s="9"/>
+        <v>168</v>
+      </c>
+      <c r="E68" s="11"/>
       <c r="F68" s="6" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="33"/>
-      <c r="B69" s="40"/>
+      <c r="B69" s="37"/>
       <c r="C69" s="6" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>125</v>
+        <v>188</v>
       </c>
       <c r="E69" s="11"/>
       <c r="F69" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="34"/>
+      <c r="B70" s="40"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="7" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="6" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="33"/>
-      <c r="B72" s="40"/>
+      <c r="B72" s="41"/>
       <c r="C72" s="6" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="6" t="s">
@@ -4097,959 +3409,447 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="33"/>
-      <c r="B73" s="40"/>
+      <c r="B73" s="41"/>
       <c r="C73" s="6" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="33"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="6" t="s">
+      <c r="B74" s="45"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="15"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="33"/>
+      <c r="B75" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="33"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E76" s="11"/>
+      <c r="F76" s="6" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="34"/>
-      <c r="B75" s="41"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="19"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B76" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E76" s="18"/>
-      <c r="F76" s="7" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="33"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B77" s="45"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="15"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="33"/>
-      <c r="B78" s="44"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="15"/>
+      <c r="B78" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E78" s="11"/>
+      <c r="F78" s="6" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="33"/>
-      <c r="B79" s="40" t="s">
-        <v>365</v>
-      </c>
+      <c r="B79" s="41"/>
       <c r="C79" s="6" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E79" s="9"/>
+        <v>272</v>
+      </c>
+      <c r="E79" s="11"/>
       <c r="F79" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="33"/>
-      <c r="B80" s="40"/>
-      <c r="C80" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="6" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="34"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="19"/>
+    </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="33"/>
-      <c r="B81" s="40"/>
-      <c r="E81" s="9"/>
+      <c r="A81" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="33"/>
-      <c r="B82" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E82" s="17"/>
-      <c r="F82" s="13" t="s">
-        <v>98</v>
+      <c r="B82" s="41"/>
+      <c r="C82" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="33"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="B83" s="45"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="33"/>
-      <c r="B84" s="36"/>
+      <c r="B84" s="44" t="s">
+        <v>183</v>
+      </c>
       <c r="C84" s="6" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E84" s="1"/>
+        <v>164</v>
+      </c>
       <c r="F84" s="6" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="33"/>
-      <c r="B85" s="36"/>
+      <c r="B85" s="41"/>
       <c r="C85" s="6" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E85" s="9"/>
+        <v>235</v>
+      </c>
       <c r="F85" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="33"/>
-      <c r="B86" s="36"/>
+      <c r="B86" s="41"/>
       <c r="C86" s="6" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E86" s="12"/>
+        <v>176</v>
+      </c>
       <c r="F86" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="33"/>
-      <c r="B87" s="36"/>
+      <c r="B87" s="41"/>
       <c r="C87" s="6" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E87" s="9"/>
+        <v>178</v>
+      </c>
       <c r="F87" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="33"/>
-      <c r="B88" s="36"/>
+      <c r="B88" s="41"/>
       <c r="C88" s="6" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E88" s="9"/>
+        <v>180</v>
+      </c>
       <c r="F88" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="33"/>
-      <c r="B89" s="36"/>
+      <c r="B89" s="41"/>
       <c r="C89" s="6" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E89" s="11"/>
+        <v>186</v>
+      </c>
       <c r="F89" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="33"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E90" s="11"/>
-      <c r="F90" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B90" s="41"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="33"/>
-      <c r="B91" s="37"/>
+      <c r="B91" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="33"/>
-      <c r="B92" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E92" s="17"/>
-      <c r="F92" s="13" t="s">
-        <v>98</v>
+      <c r="B92" s="41"/>
+      <c r="C92" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="33"/>
-      <c r="B93" s="36"/>
+      <c r="B93" s="41"/>
       <c r="C93" s="6" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E93" s="1"/>
+        <v>213</v>
+      </c>
       <c r="F93" s="6" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="33"/>
-      <c r="B94" s="36"/>
+      <c r="B94" s="41"/>
       <c r="C94" s="6" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E94" s="1"/>
+        <v>208</v>
+      </c>
       <c r="F94" s="6" t="s">
-        <v>118</v>
+        <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="33"/>
-      <c r="B95" s="36"/>
+      <c r="B95" s="41"/>
       <c r="C95" s="6" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E95" s="1"/>
+        <v>215</v>
+      </c>
       <c r="F95" s="6" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="33"/>
-      <c r="B96" s="36"/>
+      <c r="B96" s="41"/>
       <c r="C96" s="6" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E96" s="12"/>
+        <v>210</v>
+      </c>
       <c r="F96" s="6" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="33"/>
-      <c r="B97" s="36"/>
+      <c r="B97" s="41"/>
       <c r="C97" s="6" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E97" s="21"/>
+        <v>219</v>
+      </c>
       <c r="F97" s="6" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="33"/>
-      <c r="B98" s="36"/>
+      <c r="B98" s="41"/>
       <c r="C98" s="6" t="s">
-        <v>196</v>
+        <v>275</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E98" s="21"/>
+        <v>265</v>
+      </c>
       <c r="F98" s="6" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="33"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="6" t="s">
-        <v>140</v>
-      </c>
+      <c r="B99" s="41"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="33"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="34"/>
-      <c r="B101" s="39"/>
+      <c r="B100" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="33"/>
+      <c r="B101" s="41"/>
+      <c r="C101" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B102" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E102" s="8"/>
-      <c r="F102" s="7" t="s">
-        <v>118</v>
+      <c r="A102" s="33"/>
+      <c r="B102" s="41"/>
+      <c r="C102" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="33"/>
-      <c r="B103" s="40"/>
+      <c r="B103" s="41"/>
       <c r="C103" s="6" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E103" s="11"/>
+        <v>273</v>
+      </c>
       <c r="F103" s="6" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="33"/>
-      <c r="B104" s="40"/>
-      <c r="C104" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E104" s="11"/>
-      <c r="F104" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B104" s="41"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="33"/>
-      <c r="B105" s="44"/>
-      <c r="C105" s="15"/>
-      <c r="D105" s="15"/>
-      <c r="E105" s="16"/>
-      <c r="F105" s="15"/>
+      <c r="B105" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="33"/>
-      <c r="B106" s="43" t="s">
-        <v>283</v>
-      </c>
+      <c r="B106" s="41"/>
       <c r="C106" s="6" t="s">
-        <v>284</v>
+        <v>239</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E106" s="11"/>
+        <v>240</v>
+      </c>
       <c r="F106" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="33"/>
-      <c r="B107" s="40"/>
-      <c r="C107" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E107" s="11"/>
-      <c r="F107" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="33"/>
-      <c r="B108" s="40"/>
-      <c r="C108" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="E108" s="11"/>
-      <c r="F108" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="33"/>
-      <c r="B109" s="44"/>
-      <c r="E109" s="11"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="33"/>
-      <c r="B110" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C110" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E110" s="17"/>
-      <c r="F110" s="13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="33"/>
-      <c r="B111" s="40"/>
-      <c r="C111" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E111" s="11"/>
-      <c r="F111" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="33"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="15"/>
-      <c r="D112" s="15"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="15"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="33"/>
-      <c r="B113" s="43" t="s">
-        <v>354</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E113" s="11"/>
-      <c r="F113" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="33"/>
-      <c r="B114" s="40"/>
-      <c r="C114" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E114" s="11"/>
-      <c r="F114" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="34"/>
-      <c r="B115" s="41"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="19"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="B116" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="33"/>
-      <c r="B117" s="40"/>
-      <c r="C117" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="33"/>
-      <c r="B118" s="44"/>
-      <c r="C118" s="15"/>
-      <c r="D118" s="15"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="15"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="33"/>
-      <c r="B119" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="33"/>
-      <c r="B120" s="40"/>
-      <c r="C120" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="33"/>
-      <c r="B121" s="40"/>
-      <c r="C121" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="33"/>
-      <c r="B122" s="40"/>
-      <c r="C122" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="33"/>
-      <c r="B123" s="40"/>
-      <c r="C123" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="33"/>
-      <c r="B124" s="40"/>
-      <c r="C124" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="33"/>
-      <c r="B125" s="40"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="33"/>
-      <c r="B126" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="C126" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="E126" s="13"/>
-      <c r="F126" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="33"/>
-      <c r="B127" s="40"/>
-      <c r="C127" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="33"/>
-      <c r="B128" s="40"/>
-      <c r="C128" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="33"/>
-      <c r="B129" s="40"/>
-      <c r="C129" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="33"/>
-      <c r="B130" s="40"/>
-      <c r="C130" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="33"/>
-      <c r="B131" s="40"/>
-      <c r="C131" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="33"/>
-      <c r="B132" s="40"/>
-      <c r="C132" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="33"/>
-      <c r="B133" s="40"/>
-      <c r="C133" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="33"/>
-      <c r="B134" s="40"/>
-      <c r="C134" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="33"/>
-      <c r="B135" s="40"/>
-      <c r="C135" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="33"/>
-      <c r="B136" s="40"/>
-      <c r="C136" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="33"/>
-      <c r="B137" s="40"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="33"/>
-      <c r="B138" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="C138" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E138" s="13"/>
-      <c r="F138" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="33"/>
-      <c r="B139" s="40"/>
-      <c r="C139" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="33"/>
-      <c r="B140" s="40"/>
-      <c r="C140" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="33"/>
-      <c r="B141" s="40"/>
-      <c r="C141" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="33"/>
-      <c r="B142" s="40"/>
-      <c r="C142" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="33"/>
-      <c r="B143" s="40"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="33"/>
-      <c r="B144" s="43" t="s">
-        <v>321</v>
-      </c>
-      <c r="C144" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="E144" s="13"/>
-      <c r="F144" s="13" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="33"/>
-      <c r="B145" s="40"/>
-      <c r="C145" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>360</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="A116:A145"/>
-    <mergeCell ref="A2:A43"/>
+  <mergeCells count="21">
+    <mergeCell ref="B100:B104"/>
+    <mergeCell ref="A45:A70"/>
+    <mergeCell ref="B51:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="A81:A106"/>
+    <mergeCell ref="A2:A22"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="A23:A44"/>
+    <mergeCell ref="B33:B44"/>
     <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B119:B125"/>
-    <mergeCell ref="B126:B137"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B138:B143"/>
-    <mergeCell ref="A76:A101"/>
-    <mergeCell ref="B82:B91"/>
-    <mergeCell ref="B92:B101"/>
-    <mergeCell ref="A102:A115"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B91:B99"/>
+    <mergeCell ref="B81:B83"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_Bio_Brownfield_Höchst/Datenbank.xlsx
+++ b/Methane/Methane_Bio_Brownfield_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_Brownfield_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E81AA1E-B5C7-427A-9FF7-8AF4D4398F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256594FB-E40B-44DE-9BB7-58814B5466EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1169,6 +1169,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1211,10 +1215,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1549,10 +1549,10 @@
       <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1569,8 +1569,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="41"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -1585,8 +1585,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="41"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1601,8 +1601,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1617,8 +1617,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="41"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1633,8 +1633,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1649,8 +1649,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="44" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="46" t="s">
         <v>243</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -1668,8 +1668,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="41"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
@@ -1684,8 +1684,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1700,8 +1700,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="41"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1716,8 +1716,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="41"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
@@ -1732,8 +1732,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="41"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="6" t="s">
         <v>228</v>
       </c>
@@ -1748,8 +1748,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="41"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="43"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
@@ -1764,8 +1764,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
-      <c r="B15" s="45"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
@@ -1780,10 +1780,10 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="38" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -1800,8 +1800,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="37"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
@@ -1816,8 +1816,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="37"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
@@ -1832,8 +1832,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="37"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="6" t="s">
         <v>20</v>
       </c>
@@ -1848,8 +1848,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="37"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="6" t="s">
         <v>35</v>
       </c>
@@ -1864,8 +1864,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="37"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
@@ -1880,8 +1880,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="37"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
@@ -1896,8 +1896,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="40"/>
       <c r="C23" s="15" t="s">
         <v>88</v>
       </c>
@@ -1912,8 +1912,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="39" t="s">
+      <c r="A24" s="35"/>
+      <c r="B24" s="41" t="s">
         <v>200</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1930,8 +1930,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="41"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="43"/>
       <c r="C25" s="6" t="s">
         <v>21</v>
       </c>
@@ -1947,8 +1947,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="41"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="43"/>
       <c r="C26" s="6" t="s">
         <v>16</v>
       </c>
@@ -1963,8 +1963,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="41"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="43"/>
       <c r="C27" s="6" t="s">
         <v>17</v>
       </c>
@@ -1979,8 +1979,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="41"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="43"/>
       <c r="C28" s="6" t="s">
         <v>35</v>
       </c>
@@ -1995,8 +1995,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="41"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
@@ -2011,8 +2011,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="41"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="6" t="s">
         <v>89</v>
       </c>
@@ -2027,8 +2027,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="41"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="43"/>
       <c r="C31" s="6" t="s">
         <v>88</v>
       </c>
@@ -2043,8 +2043,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="41"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="6" t="s">
         <v>13</v>
       </c>
@@ -2059,8 +2059,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="34"/>
-      <c r="B33" s="42"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="44"/>
       <c r="C33" s="19" t="s">
         <v>15</v>
       </c>
@@ -2075,10 +2075,10 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="32" t="s">
         <v>73</v>
       </c>
       <c r="C34" s="25" t="s">
@@ -2087,7 +2087,7 @@
       <c r="D34" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="47">
+      <c r="E34" s="33">
         <v>0.1699</v>
       </c>
       <c r="F34" s="25" t="s">
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="35"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="30" t="s">
         <v>279</v>
       </c>
@@ -2113,8 +2113,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="39" t="s">
+      <c r="A36" s="35"/>
+      <c r="B36" s="41" t="s">
         <v>4</v>
       </c>
       <c r="C36" s="13" t="s">
@@ -2131,8 +2131,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="37"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="39"/>
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
@@ -2147,8 +2147,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="39"/>
       <c r="C38" s="6" t="s">
         <v>17</v>
       </c>
@@ -2163,8 +2163,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="39"/>
       <c r="C39" s="6" t="s">
         <v>18</v>
       </c>
@@ -2179,8 +2179,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="39"/>
       <c r="C40" s="6" t="s">
         <v>13</v>
       </c>
@@ -2195,8 +2195,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="37"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="39"/>
       <c r="C41" s="6" t="s">
         <v>68</v>
       </c>
@@ -2211,8 +2211,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="38"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="40"/>
       <c r="C42" s="15" t="s">
         <v>15</v>
       </c>
@@ -2227,8 +2227,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="39" t="s">
+      <c r="A43" s="35"/>
+      <c r="B43" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="13" t="s">
@@ -2245,8 +2245,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="33"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="39"/>
       <c r="C44" s="6" t="s">
         <v>10</v>
       </c>
@@ -2261,8 +2261,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="37"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="6" t="s">
         <v>17</v>
       </c>
@@ -2277,8 +2277,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="6" t="s">
         <v>18</v>
       </c>
@@ -2293,8 +2293,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="37"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="6" t="s">
         <v>13</v>
       </c>
@@ -2309,8 +2309,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="6" t="s">
         <v>68</v>
       </c>
@@ -2325,8 +2325,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="34"/>
-      <c r="B49" s="40"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="42"/>
       <c r="C49" s="19" t="s">
         <v>15</v>
       </c>
@@ -2341,7 +2341,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="34" t="s">
         <v>76</v>
       </c>
       <c r="B50" s="24" t="s">
@@ -2354,14 +2354,14 @@
         <v>78</v>
       </c>
       <c r="E50" s="26">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="27" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="34"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="4" t="s">
         <v>276</v>
       </c>
@@ -2450,10 +2450,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -2468,8 +2468,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="41"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="6" t="s">
         <v>107</v>
       </c>
@@ -2482,8 +2482,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="41"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
@@ -2496,8 +2496,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="6" t="s">
         <v>138</v>
       </c>
@@ -2510,8 +2510,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="41"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
@@ -2524,8 +2524,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="6" t="s">
         <v>155</v>
       </c>
@@ -2538,8 +2538,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="41"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="6" t="s">
         <v>195</v>
       </c>
@@ -2552,8 +2552,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="41"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
@@ -2566,8 +2566,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="6" t="s">
         <v>187</v>
       </c>
@@ -2580,13 +2580,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="41"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="43"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="44" t="s">
+      <c r="A12" s="35"/>
+      <c r="B12" s="46" t="s">
         <v>243</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -2601,8 +2601,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="41"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="6" t="s">
         <v>229</v>
       </c>
@@ -2615,8 +2615,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="41"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="43"/>
       <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
@@ -2629,8 +2629,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="41"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="6" t="s">
         <v>230</v>
       </c>
@@ -2643,8 +2643,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="41"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
@@ -2657,8 +2657,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="41"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="6" t="s">
         <v>141</v>
       </c>
@@ -2671,8 +2671,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="41"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="6" t="s">
         <v>155</v>
       </c>
@@ -2685,8 +2685,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="41"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="6" t="s">
         <v>195</v>
       </c>
@@ -2699,8 +2699,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="41"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="6" t="s">
         <v>167</v>
       </c>
@@ -2713,8 +2713,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="41"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="6" t="s">
         <v>187</v>
       </c>
@@ -2727,18 +2727,18 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="33"/>
-      <c r="B22" s="45"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="38" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2753,8 +2753,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="37"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="6" t="s">
         <v>111</v>
       </c>
@@ -2767,8 +2767,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="37"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="6" t="s">
         <v>135</v>
       </c>
@@ -2781,8 +2781,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="37"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="6" t="s">
         <v>136</v>
       </c>
@@ -2795,8 +2795,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="37"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="6" t="s">
         <v>141</v>
       </c>
@@ -2809,8 +2809,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="37"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="6" t="s">
         <v>155</v>
       </c>
@@ -2823,8 +2823,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="37"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="6" t="s">
         <v>195</v>
       </c>
@@ -2837,8 +2837,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="37"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="6" t="s">
         <v>167</v>
       </c>
@@ -2851,8 +2851,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="37"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="6" t="s">
         <v>187</v>
       </c>
@@ -2865,16 +2865,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="38"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="40"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
       <c r="F32" s="15"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="39" t="s">
+      <c r="A33" s="35"/>
+      <c r="B33" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -2889,8 +2889,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="6" t="s">
         <v>113</v>
       </c>
@@ -2903,8 +2903,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="33"/>
-      <c r="B35" s="41"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="43"/>
       <c r="C35" s="6" t="s">
         <v>111</v>
       </c>
@@ -2917,8 +2917,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="41"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="43"/>
       <c r="C36" s="6" t="s">
         <v>107</v>
       </c>
@@ -2931,8 +2931,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="41"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="43"/>
       <c r="C37" s="6" t="s">
         <v>126</v>
       </c>
@@ -2945,8 +2945,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="41"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="43"/>
       <c r="C38" s="6" t="s">
         <v>127</v>
       </c>
@@ -2959,8 +2959,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="41"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="43"/>
       <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
@@ -2973,8 +2973,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="41"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="43"/>
       <c r="C40" s="6" t="s">
         <v>155</v>
       </c>
@@ -2987,8 +2987,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="41"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="43"/>
       <c r="C41" s="6" t="s">
         <v>195</v>
       </c>
@@ -3001,8 +3001,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="41"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="43"/>
       <c r="C42" s="6" t="s">
         <v>167</v>
       </c>
@@ -3015,8 +3015,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="41"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="43"/>
       <c r="C43" s="6" t="s">
         <v>187</v>
       </c>
@@ -3029,18 +3029,18 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="34"/>
-      <c r="B44" s="42"/>
+      <c r="A44" s="36"/>
+      <c r="B44" s="44"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="20"/>
       <c r="F44" s="19"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="43" t="s">
+      <c r="B45" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3055,8 +3055,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="41"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="43"/>
       <c r="C46" s="6" t="s">
         <v>153</v>
       </c>
@@ -3069,16 +3069,16 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="45"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="47"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="31"/>
       <c r="F47" s="15"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="41" t="s">
+      <c r="A48" s="35"/>
+      <c r="B48" s="43" t="s">
         <v>279</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3093,8 +3093,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="41"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="43"/>
       <c r="C49" s="6" t="s">
         <v>284</v>
       </c>
@@ -3107,13 +3107,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="41"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="43"/>
       <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="B51" s="39" t="s">
+      <c r="A51" s="35"/>
+      <c r="B51" s="41" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="13" t="s">
@@ -3128,8 +3128,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="6" t="s">
         <v>107</v>
       </c>
@@ -3142,8 +3142,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="33"/>
-      <c r="B53" s="37"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="39"/>
       <c r="C53" s="6" t="s">
         <v>122</v>
       </c>
@@ -3156,8 +3156,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="33"/>
-      <c r="B54" s="37"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="39"/>
       <c r="C54" s="6" t="s">
         <v>141</v>
       </c>
@@ -3170,8 +3170,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="37"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="39"/>
       <c r="C55" s="6" t="s">
         <v>155</v>
       </c>
@@ -3184,8 +3184,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="37"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="39"/>
       <c r="C56" s="6" t="s">
         <v>161</v>
       </c>
@@ -3198,8 +3198,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="37"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="39"/>
       <c r="C57" s="6" t="s">
         <v>195</v>
       </c>
@@ -3212,8 +3212,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="37"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="39"/>
       <c r="C58" s="6" t="s">
         <v>167</v>
       </c>
@@ -3226,8 +3226,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="37"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="39"/>
       <c r="C59" s="6" t="s">
         <v>187</v>
       </c>
@@ -3240,12 +3240,12 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="38"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="40"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="39" t="s">
+      <c r="A61" s="35"/>
+      <c r="B61" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -3260,8 +3260,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="37"/>
+      <c r="A62" s="35"/>
+      <c r="B62" s="39"/>
       <c r="C62" s="6" t="s">
         <v>108</v>
       </c>
@@ -3274,8 +3274,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="37"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="39"/>
       <c r="C63" s="6" t="s">
         <v>120</v>
       </c>
@@ -3288,8 +3288,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
-      <c r="B64" s="37"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="39"/>
       <c r="C64" s="6" t="s">
         <v>141</v>
       </c>
@@ -3302,8 +3302,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="37"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="39"/>
       <c r="C65" s="6" t="s">
         <v>155</v>
       </c>
@@ -3316,8 +3316,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="37"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="39"/>
       <c r="C66" s="6" t="s">
         <v>161</v>
       </c>
@@ -3330,8 +3330,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="37"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="6" t="s">
         <v>195</v>
       </c>
@@ -3344,8 +3344,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="37"/>
+      <c r="A68" s="35"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="6" t="s">
         <v>167</v>
       </c>
@@ -3358,8 +3358,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="33"/>
-      <c r="B69" s="37"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="39"/>
       <c r="C69" s="6" t="s">
         <v>187</v>
       </c>
@@ -3372,14 +3372,14 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="34"/>
-      <c r="B70" s="40"/>
+      <c r="A70" s="36"/>
+      <c r="B70" s="42"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="32" t="s">
+      <c r="A71" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="43" t="s">
+      <c r="B71" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C71" s="7" t="s">
@@ -3394,8 +3394,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33"/>
-      <c r="B72" s="41"/>
+      <c r="A72" s="35"/>
+      <c r="B72" s="43"/>
       <c r="C72" s="6" t="s">
         <v>227</v>
       </c>
@@ -3408,8 +3408,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="33"/>
-      <c r="B73" s="41"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="43"/>
       <c r="C73" s="6" t="s">
         <v>150</v>
       </c>
@@ -3422,16 +3422,16 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="33"/>
-      <c r="B74" s="45"/>
+      <c r="A74" s="35"/>
+      <c r="B74" s="47"/>
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
       <c r="E74" s="16"/>
       <c r="F74" s="15"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="33"/>
-      <c r="B75" s="44" t="s">
+      <c r="A75" s="35"/>
+      <c r="B75" s="46" t="s">
         <v>79</v>
       </c>
       <c r="C75" s="13" t="s">
@@ -3446,8 +3446,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="33"/>
-      <c r="B76" s="41"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="43"/>
       <c r="C76" s="6" t="s">
         <v>151</v>
       </c>
@@ -3460,16 +3460,16 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="33"/>
-      <c r="B77" s="45"/>
+      <c r="A77" s="35"/>
+      <c r="B77" s="47"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
       <c r="E77" s="16"/>
       <c r="F77" s="15"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="33"/>
-      <c r="B78" s="44" t="s">
+      <c r="A78" s="35"/>
+      <c r="B78" s="46" t="s">
         <v>268</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -3484,8 +3484,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="33"/>
-      <c r="B79" s="41"/>
+      <c r="A79" s="35"/>
+      <c r="B79" s="43"/>
       <c r="C79" s="6" t="s">
         <v>270</v>
       </c>
@@ -3498,18 +3498,18 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="34"/>
-      <c r="B80" s="42"/>
+      <c r="A80" s="36"/>
+      <c r="B80" s="44"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="20"/>
       <c r="F80" s="19"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="32" t="s">
+      <c r="A81" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="43" t="s">
+      <c r="B81" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
@@ -3524,8 +3524,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="33"/>
-      <c r="B82" s="41"/>
+      <c r="A82" s="35"/>
+      <c r="B82" s="43"/>
       <c r="C82" s="6" t="s">
         <v>174</v>
       </c>
@@ -3537,16 +3537,16 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="33"/>
-      <c r="B83" s="45"/>
+      <c r="A83" s="35"/>
+      <c r="B83" s="47"/>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
       <c r="F83" s="15"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="33"/>
-      <c r="B84" s="44" t="s">
+      <c r="A84" s="35"/>
+      <c r="B84" s="46" t="s">
         <v>183</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -3560,8 +3560,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="33"/>
-      <c r="B85" s="41"/>
+      <c r="A85" s="35"/>
+      <c r="B85" s="43"/>
       <c r="C85" s="6" t="s">
         <v>181</v>
       </c>
@@ -3573,8 +3573,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="33"/>
-      <c r="B86" s="41"/>
+      <c r="A86" s="35"/>
+      <c r="B86" s="43"/>
       <c r="C86" s="6" t="s">
         <v>177</v>
       </c>
@@ -3586,8 +3586,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="33"/>
-      <c r="B87" s="41"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="43"/>
       <c r="C87" s="6" t="s">
         <v>179</v>
       </c>
@@ -3599,8 +3599,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="33"/>
-      <c r="B88" s="41"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="43"/>
       <c r="C88" s="6" t="s">
         <v>182</v>
       </c>
@@ -3612,8 +3612,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="33"/>
-      <c r="B89" s="41"/>
+      <c r="A89" s="35"/>
+      <c r="B89" s="43"/>
       <c r="C89" s="6" t="s">
         <v>190</v>
       </c>
@@ -3625,12 +3625,12 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="33"/>
-      <c r="B90" s="41"/>
+      <c r="A90" s="35"/>
+      <c r="B90" s="43"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="33"/>
-      <c r="B91" s="44" t="s">
+      <c r="A91" s="35"/>
+      <c r="B91" s="46" t="s">
         <v>205</v>
       </c>
       <c r="C91" s="13" t="s">
@@ -3645,8 +3645,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="33"/>
-      <c r="B92" s="41"/>
+      <c r="A92" s="35"/>
+      <c r="B92" s="43"/>
       <c r="C92" s="6" t="s">
         <v>203</v>
       </c>
@@ -3658,8 +3658,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="33"/>
-      <c r="B93" s="41"/>
+      <c r="A93" s="35"/>
+      <c r="B93" s="43"/>
       <c r="C93" s="6" t="s">
         <v>214</v>
       </c>
@@ -3671,8 +3671,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="33"/>
-      <c r="B94" s="41"/>
+      <c r="A94" s="35"/>
+      <c r="B94" s="43"/>
       <c r="C94" s="6" t="s">
         <v>204</v>
       </c>
@@ -3684,8 +3684,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="33"/>
-      <c r="B95" s="41"/>
+      <c r="A95" s="35"/>
+      <c r="B95" s="43"/>
       <c r="C95" s="6" t="s">
         <v>216</v>
       </c>
@@ -3697,8 +3697,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="33"/>
-      <c r="B96" s="41"/>
+      <c r="A96" s="35"/>
+      <c r="B96" s="43"/>
       <c r="C96" s="6" t="s">
         <v>220</v>
       </c>
@@ -3710,8 +3710,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="33"/>
-      <c r="B97" s="41"/>
+      <c r="A97" s="35"/>
+      <c r="B97" s="43"/>
       <c r="C97" s="6" t="s">
         <v>201</v>
       </c>
@@ -3723,8 +3723,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="33"/>
-      <c r="B98" s="41"/>
+      <c r="A98" s="35"/>
+      <c r="B98" s="43"/>
       <c r="C98" s="6" t="s">
         <v>275</v>
       </c>
@@ -3736,12 +3736,12 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="33"/>
-      <c r="B99" s="41"/>
+      <c r="A99" s="35"/>
+      <c r="B99" s="43"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="33"/>
-      <c r="B100" s="44" t="s">
+      <c r="A100" s="35"/>
+      <c r="B100" s="46" t="s">
         <v>221</v>
       </c>
       <c r="C100" s="13" t="s">
@@ -3756,8 +3756,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="33"/>
-      <c r="B101" s="41"/>
+      <c r="A101" s="35"/>
+      <c r="B101" s="43"/>
       <c r="C101" s="6" t="s">
         <v>224</v>
       </c>
@@ -3769,8 +3769,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="33"/>
-      <c r="B102" s="41"/>
+      <c r="A102" s="35"/>
+      <c r="B102" s="43"/>
       <c r="C102" s="6" t="s">
         <v>232</v>
       </c>
@@ -3782,8 +3782,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="33"/>
-      <c r="B103" s="41"/>
+      <c r="A103" s="35"/>
+      <c r="B103" s="43"/>
       <c r="C103" s="6" t="s">
         <v>234</v>
       </c>
@@ -3795,12 +3795,12 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="33"/>
-      <c r="B104" s="41"/>
+      <c r="A104" s="35"/>
+      <c r="B104" s="43"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="33"/>
-      <c r="B105" s="44" t="s">
+      <c r="A105" s="35"/>
+      <c r="B105" s="46" t="s">
         <v>236</v>
       </c>
       <c r="C105" s="13" t="s">
@@ -3815,8 +3815,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="33"/>
-      <c r="B106" s="41"/>
+      <c r="A106" s="35"/>
+      <c r="B106" s="43"/>
       <c r="C106" s="6" t="s">
         <v>239</v>
       </c>
@@ -3829,14 +3829,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B100:B104"/>
-    <mergeCell ref="A45:A70"/>
-    <mergeCell ref="B51:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="A71:A80"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B105:B106"/>
     <mergeCell ref="A81:A106"/>
     <mergeCell ref="A2:A22"/>
@@ -3850,6 +3842,14 @@
     <mergeCell ref="B84:B90"/>
     <mergeCell ref="B91:B99"/>
     <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B100:B104"/>
+    <mergeCell ref="A45:A70"/>
+    <mergeCell ref="B51:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_Bio_Brownfield_Höchst/Datenbank.xlsx
+++ b/Methane/Methane_Bio_Brownfield_Höchst/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_Brownfield_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_Bio_Brownfield_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256594FB-E40B-44DE-9BB7-58814B5466EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ED61C0-F438-4206-91D5-277F3D5212C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -995,10 +995,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1130,41 +1130,41 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1180,9 +1180,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1552,7 +1549,7 @@
       <c r="A2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1570,7 +1567,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="35"/>
-      <c r="B3" s="43"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -1586,7 +1583,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="B4" s="43"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1594,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>83</v>
@@ -1602,7 +1599,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="35"/>
-      <c r="B5" s="43"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1618,7 +1615,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
-      <c r="B6" s="43"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1634,7 +1631,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1650,7 +1647,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="45" t="s">
         <v>243</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -1669,7 +1666,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
-      <c r="B9" s="43"/>
+      <c r="B9" s="42"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
@@ -1685,7 +1682,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
-      <c r="B10" s="43"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1701,7 +1698,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="35"/>
-      <c r="B11" s="43"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1717,7 +1714,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="35"/>
-      <c r="B12" s="43"/>
+      <c r="B12" s="42"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
@@ -1733,7 +1730,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="35"/>
-      <c r="B13" s="43"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="6" t="s">
         <v>228</v>
       </c>
@@ -1749,7 +1746,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="35"/>
-      <c r="B14" s="43"/>
+      <c r="B14" s="42"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
@@ -1765,7 +1762,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="35"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="46"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
@@ -1783,7 +1780,7 @@
       <c r="A16" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="37" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -1801,7 +1798,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="35"/>
-      <c r="B17" s="39"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
@@ -1817,7 +1814,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="35"/>
-      <c r="B18" s="39"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
@@ -1833,7 +1830,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="35"/>
-      <c r="B19" s="39"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="6" t="s">
         <v>20</v>
       </c>
@@ -1849,7 +1846,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="35"/>
-      <c r="B20" s="39"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="6" t="s">
         <v>35</v>
       </c>
@@ -1865,7 +1862,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="35"/>
-      <c r="B21" s="39"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
@@ -1881,7 +1878,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="35"/>
-      <c r="B22" s="39"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
@@ -1897,7 +1894,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="35"/>
-      <c r="B23" s="40"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="15" t="s">
         <v>88</v>
       </c>
@@ -1913,7 +1910,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="35"/>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>200</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1931,7 +1928,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35"/>
-      <c r="B25" s="43"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="6" t="s">
         <v>21</v>
       </c>
@@ -1948,7 +1945,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="35"/>
-      <c r="B26" s="43"/>
+      <c r="B26" s="42"/>
       <c r="C26" s="6" t="s">
         <v>16</v>
       </c>
@@ -1964,7 +1961,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="35"/>
-      <c r="B27" s="43"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="6" t="s">
         <v>17</v>
       </c>
@@ -1980,7 +1977,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="35"/>
-      <c r="B28" s="43"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="6" t="s">
         <v>35</v>
       </c>
@@ -1996,7 +1993,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="35"/>
-      <c r="B29" s="43"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
@@ -2012,7 +2009,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="35"/>
-      <c r="B30" s="43"/>
+      <c r="B30" s="42"/>
       <c r="C30" s="6" t="s">
         <v>89</v>
       </c>
@@ -2028,7 +2025,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="35"/>
-      <c r="B31" s="43"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="6" t="s">
         <v>88</v>
       </c>
@@ -2044,7 +2041,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="35"/>
-      <c r="B32" s="43"/>
+      <c r="B32" s="42"/>
       <c r="C32" s="6" t="s">
         <v>13</v>
       </c>
@@ -2060,7 +2057,7 @@
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="36"/>
-      <c r="B33" s="44"/>
+      <c r="B33" s="43"/>
       <c r="C33" s="19" t="s">
         <v>15</v>
       </c>
@@ -2095,7 +2092,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="30" t="s">
         <v>279</v>
       </c>
@@ -2114,7 +2111,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="35"/>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>4</v>
       </c>
       <c r="C36" s="13" t="s">
@@ -2132,7 +2129,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="35"/>
-      <c r="B37" s="39"/>
+      <c r="B37" s="38"/>
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
@@ -2148,7 +2145,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="35"/>
-      <c r="B38" s="39"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="6" t="s">
         <v>17</v>
       </c>
@@ -2164,7 +2161,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="35"/>
-      <c r="B39" s="39"/>
+      <c r="B39" s="38"/>
       <c r="C39" s="6" t="s">
         <v>18</v>
       </c>
@@ -2180,7 +2177,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="35"/>
-      <c r="B40" s="39"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="6" t="s">
         <v>13</v>
       </c>
@@ -2196,7 +2193,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="35"/>
-      <c r="B41" s="39"/>
+      <c r="B41" s="38"/>
       <c r="C41" s="6" t="s">
         <v>68</v>
       </c>
@@ -2212,7 +2209,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="35"/>
-      <c r="B42" s="40"/>
+      <c r="B42" s="39"/>
       <c r="C42" s="15" t="s">
         <v>15</v>
       </c>
@@ -2228,7 +2225,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="35"/>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="13" t="s">
@@ -2246,7 +2243,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="35"/>
-      <c r="B44" s="39"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="6" t="s">
         <v>10</v>
       </c>
@@ -2262,7 +2259,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="35"/>
-      <c r="B45" s="39"/>
+      <c r="B45" s="38"/>
       <c r="C45" s="6" t="s">
         <v>17</v>
       </c>
@@ -2278,7 +2275,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="35"/>
-      <c r="B46" s="39"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="6" t="s">
         <v>18</v>
       </c>
@@ -2294,7 +2291,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="35"/>
-      <c r="B47" s="39"/>
+      <c r="B47" s="38"/>
       <c r="C47" s="6" t="s">
         <v>13</v>
       </c>
@@ -2310,7 +2307,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="35"/>
-      <c r="B48" s="39"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="6" t="s">
         <v>68</v>
       </c>
@@ -2326,7 +2323,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="36"/>
-      <c r="B49" s="42"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="19" t="s">
         <v>15</v>
       </c>
@@ -2453,7 +2450,7 @@
       <c r="A2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -2469,7 +2466,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="35"/>
-      <c r="B3" s="43"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="6" t="s">
         <v>107</v>
       </c>
@@ -2483,7 +2480,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="B4" s="43"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
@@ -2497,7 +2494,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="35"/>
-      <c r="B5" s="43"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="6" t="s">
         <v>138</v>
       </c>
@@ -2511,7 +2508,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
-      <c r="B6" s="43"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
@@ -2525,7 +2522,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="6" t="s">
         <v>155</v>
       </c>
@@ -2539,7 +2536,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
-      <c r="B8" s="43"/>
+      <c r="B8" s="42"/>
       <c r="C8" s="6" t="s">
         <v>195</v>
       </c>
@@ -2553,7 +2550,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
-      <c r="B9" s="43"/>
+      <c r="B9" s="42"/>
       <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
@@ -2567,7 +2564,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
-      <c r="B10" s="43"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="6" t="s">
         <v>187</v>
       </c>
@@ -2581,12 +2578,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="35"/>
-      <c r="B11" s="43"/>
+      <c r="B11" s="42"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="35"/>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="45" t="s">
         <v>243</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -2602,7 +2599,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="35"/>
-      <c r="B13" s="43"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="6" t="s">
         <v>229</v>
       </c>
@@ -2616,7 +2613,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="35"/>
-      <c r="B14" s="43"/>
+      <c r="B14" s="42"/>
       <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
@@ -2630,7 +2627,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="35"/>
-      <c r="B15" s="43"/>
+      <c r="B15" s="42"/>
       <c r="C15" s="6" t="s">
         <v>230</v>
       </c>
@@ -2644,7 +2641,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="35"/>
-      <c r="B16" s="43"/>
+      <c r="B16" s="42"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
@@ -2658,7 +2655,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="35"/>
-      <c r="B17" s="43"/>
+      <c r="B17" s="42"/>
       <c r="C17" s="6" t="s">
         <v>141</v>
       </c>
@@ -2672,7 +2669,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="35"/>
-      <c r="B18" s="43"/>
+      <c r="B18" s="42"/>
       <c r="C18" s="6" t="s">
         <v>155</v>
       </c>
@@ -2686,7 +2683,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="35"/>
-      <c r="B19" s="43"/>
+      <c r="B19" s="42"/>
       <c r="C19" s="6" t="s">
         <v>195</v>
       </c>
@@ -2700,7 +2697,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="35"/>
-      <c r="B20" s="43"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="6" t="s">
         <v>167</v>
       </c>
@@ -2714,7 +2711,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="35"/>
-      <c r="B21" s="43"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="6" t="s">
         <v>187</v>
       </c>
@@ -2728,7 +2725,7 @@
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35"/>
-      <c r="B22" s="47"/>
+      <c r="B22" s="46"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
@@ -2738,7 +2735,7 @@
       <c r="A23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="37" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2754,7 +2751,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="35"/>
-      <c r="B24" s="39"/>
+      <c r="B24" s="38"/>
       <c r="C24" s="6" t="s">
         <v>111</v>
       </c>
@@ -2768,7 +2765,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35"/>
-      <c r="B25" s="39"/>
+      <c r="B25" s="38"/>
       <c r="C25" s="6" t="s">
         <v>135</v>
       </c>
@@ -2782,7 +2779,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="35"/>
-      <c r="B26" s="39"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="6" t="s">
         <v>136</v>
       </c>
@@ -2796,7 +2793,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="35"/>
-      <c r="B27" s="39"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="6" t="s">
         <v>141</v>
       </c>
@@ -2810,7 +2807,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="35"/>
-      <c r="B28" s="39"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="6" t="s">
         <v>155</v>
       </c>
@@ -2824,7 +2821,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="35"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="38"/>
       <c r="C29" s="6" t="s">
         <v>195</v>
       </c>
@@ -2838,7 +2835,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="35"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="38"/>
       <c r="C30" s="6" t="s">
         <v>167</v>
       </c>
@@ -2852,7 +2849,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="35"/>
-      <c r="B31" s="39"/>
+      <c r="B31" s="38"/>
       <c r="C31" s="6" t="s">
         <v>187</v>
       </c>
@@ -2866,7 +2863,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="35"/>
-      <c r="B32" s="40"/>
+      <c r="B32" s="39"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
@@ -2874,7 +2871,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="35"/>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -2890,7 +2887,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="35"/>
-      <c r="B34" s="39"/>
+      <c r="B34" s="38"/>
       <c r="C34" s="6" t="s">
         <v>113</v>
       </c>
@@ -2904,7 +2901,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="35"/>
-      <c r="B35" s="43"/>
+      <c r="B35" s="42"/>
       <c r="C35" s="6" t="s">
         <v>111</v>
       </c>
@@ -2918,7 +2915,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="35"/>
-      <c r="B36" s="43"/>
+      <c r="B36" s="42"/>
       <c r="C36" s="6" t="s">
         <v>107</v>
       </c>
@@ -2932,7 +2929,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="35"/>
-      <c r="B37" s="43"/>
+      <c r="B37" s="42"/>
       <c r="C37" s="6" t="s">
         <v>126</v>
       </c>
@@ -2946,7 +2943,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="35"/>
-      <c r="B38" s="43"/>
+      <c r="B38" s="42"/>
       <c r="C38" s="6" t="s">
         <v>127</v>
       </c>
@@ -2960,7 +2957,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="35"/>
-      <c r="B39" s="43"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
@@ -2974,7 +2971,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="35"/>
-      <c r="B40" s="43"/>
+      <c r="B40" s="42"/>
       <c r="C40" s="6" t="s">
         <v>155</v>
       </c>
@@ -2988,7 +2985,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="35"/>
-      <c r="B41" s="43"/>
+      <c r="B41" s="42"/>
       <c r="C41" s="6" t="s">
         <v>195</v>
       </c>
@@ -3002,7 +2999,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="35"/>
-      <c r="B42" s="43"/>
+      <c r="B42" s="42"/>
       <c r="C42" s="6" t="s">
         <v>167</v>
       </c>
@@ -3016,7 +3013,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="35"/>
-      <c r="B43" s="43"/>
+      <c r="B43" s="42"/>
       <c r="C43" s="6" t="s">
         <v>187</v>
       </c>
@@ -3030,7 +3027,7 @@
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="36"/>
-      <c r="B44" s="44"/>
+      <c r="B44" s="43"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="20"/>
@@ -3040,7 +3037,7 @@
       <c r="A45" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="45" t="s">
+      <c r="B45" s="44" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3056,7 +3053,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="35"/>
-      <c r="B46" s="43"/>
+      <c r="B46" s="42"/>
       <c r="C46" s="6" t="s">
         <v>153</v>
       </c>
@@ -3070,7 +3067,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="35"/>
-      <c r="B47" s="47"/>
+      <c r="B47" s="46"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="31"/>
@@ -3078,7 +3075,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="35"/>
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="42" t="s">
         <v>279</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3094,7 +3091,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="35"/>
-      <c r="B49" s="43"/>
+      <c r="B49" s="42"/>
       <c r="C49" s="6" t="s">
         <v>284</v>
       </c>
@@ -3108,12 +3105,12 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="35"/>
-      <c r="B50" s="43"/>
+      <c r="B50" s="42"/>
       <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="35"/>
-      <c r="B51" s="41" t="s">
+      <c r="B51" s="40" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="13" t="s">
@@ -3129,7 +3126,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="35"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="6" t="s">
         <v>107</v>
       </c>
@@ -3143,7 +3140,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="35"/>
-      <c r="B53" s="39"/>
+      <c r="B53" s="38"/>
       <c r="C53" s="6" t="s">
         <v>122</v>
       </c>
@@ -3157,7 +3154,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="35"/>
-      <c r="B54" s="39"/>
+      <c r="B54" s="38"/>
       <c r="C54" s="6" t="s">
         <v>141</v>
       </c>
@@ -3171,7 +3168,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="35"/>
-      <c r="B55" s="39"/>
+      <c r="B55" s="38"/>
       <c r="C55" s="6" t="s">
         <v>155</v>
       </c>
@@ -3185,7 +3182,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="35"/>
-      <c r="B56" s="39"/>
+      <c r="B56" s="38"/>
       <c r="C56" s="6" t="s">
         <v>161</v>
       </c>
@@ -3199,7 +3196,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="35"/>
-      <c r="B57" s="39"/>
+      <c r="B57" s="38"/>
       <c r="C57" s="6" t="s">
         <v>195</v>
       </c>
@@ -3213,7 +3210,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="35"/>
-      <c r="B58" s="39"/>
+      <c r="B58" s="38"/>
       <c r="C58" s="6" t="s">
         <v>167</v>
       </c>
@@ -3227,7 +3224,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="35"/>
-      <c r="B59" s="39"/>
+      <c r="B59" s="38"/>
       <c r="C59" s="6" t="s">
         <v>187</v>
       </c>
@@ -3241,11 +3238,11 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="35"/>
-      <c r="B60" s="40"/>
+      <c r="B60" s="39"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="35"/>
-      <c r="B61" s="41" t="s">
+      <c r="B61" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -3261,7 +3258,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="35"/>
-      <c r="B62" s="39"/>
+      <c r="B62" s="38"/>
       <c r="C62" s="6" t="s">
         <v>108</v>
       </c>
@@ -3275,7 +3272,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="35"/>
-      <c r="B63" s="39"/>
+      <c r="B63" s="38"/>
       <c r="C63" s="6" t="s">
         <v>120</v>
       </c>
@@ -3289,7 +3286,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="35"/>
-      <c r="B64" s="39"/>
+      <c r="B64" s="38"/>
       <c r="C64" s="6" t="s">
         <v>141</v>
       </c>
@@ -3303,7 +3300,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="35"/>
-      <c r="B65" s="39"/>
+      <c r="B65" s="38"/>
       <c r="C65" s="6" t="s">
         <v>155</v>
       </c>
@@ -3317,7 +3314,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="35"/>
-      <c r="B66" s="39"/>
+      <c r="B66" s="38"/>
       <c r="C66" s="6" t="s">
         <v>161</v>
       </c>
@@ -3331,7 +3328,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="35"/>
-      <c r="B67" s="39"/>
+      <c r="B67" s="38"/>
       <c r="C67" s="6" t="s">
         <v>195</v>
       </c>
@@ -3345,7 +3342,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="35"/>
-      <c r="B68" s="39"/>
+      <c r="B68" s="38"/>
       <c r="C68" s="6" t="s">
         <v>167</v>
       </c>
@@ -3359,7 +3356,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="35"/>
-      <c r="B69" s="39"/>
+      <c r="B69" s="38"/>
       <c r="C69" s="6" t="s">
         <v>187</v>
       </c>
@@ -3373,13 +3370,13 @@
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="36"/>
-      <c r="B70" s="42"/>
+      <c r="B70" s="41"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="44" t="s">
         <v>73</v>
       </c>
       <c r="C71" s="7" t="s">
@@ -3395,7 +3392,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="35"/>
-      <c r="B72" s="43"/>
+      <c r="B72" s="42"/>
       <c r="C72" s="6" t="s">
         <v>227</v>
       </c>
@@ -3409,7 +3406,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="35"/>
-      <c r="B73" s="43"/>
+      <c r="B73" s="42"/>
       <c r="C73" s="6" t="s">
         <v>150</v>
       </c>
@@ -3423,7 +3420,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="35"/>
-      <c r="B74" s="47"/>
+      <c r="B74" s="46"/>
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
       <c r="E74" s="16"/>
@@ -3431,7 +3428,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="35"/>
-      <c r="B75" s="46" t="s">
+      <c r="B75" s="45" t="s">
         <v>79</v>
       </c>
       <c r="C75" s="13" t="s">
@@ -3447,7 +3444,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="35"/>
-      <c r="B76" s="43"/>
+      <c r="B76" s="42"/>
       <c r="C76" s="6" t="s">
         <v>151</v>
       </c>
@@ -3461,7 +3458,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="35"/>
-      <c r="B77" s="47"/>
+      <c r="B77" s="46"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
       <c r="E77" s="16"/>
@@ -3469,7 +3466,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="35"/>
-      <c r="B78" s="46" t="s">
+      <c r="B78" s="45" t="s">
         <v>268</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -3485,7 +3482,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="35"/>
-      <c r="B79" s="43"/>
+      <c r="B79" s="42"/>
       <c r="C79" s="6" t="s">
         <v>270</v>
       </c>
@@ -3499,7 +3496,7 @@
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="36"/>
-      <c r="B80" s="44"/>
+      <c r="B80" s="43"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="20"/>
@@ -3509,7 +3506,7 @@
       <c r="A81" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="45" t="s">
+      <c r="B81" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
@@ -3525,7 +3522,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="35"/>
-      <c r="B82" s="43"/>
+      <c r="B82" s="42"/>
       <c r="C82" s="6" t="s">
         <v>174</v>
       </c>
@@ -3538,7 +3535,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="35"/>
-      <c r="B83" s="47"/>
+      <c r="B83" s="46"/>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
@@ -3546,7 +3543,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="35"/>
-      <c r="B84" s="46" t="s">
+      <c r="B84" s="45" t="s">
         <v>183</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -3561,7 +3558,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="35"/>
-      <c r="B85" s="43"/>
+      <c r="B85" s="42"/>
       <c r="C85" s="6" t="s">
         <v>181</v>
       </c>
@@ -3574,7 +3571,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="35"/>
-      <c r="B86" s="43"/>
+      <c r="B86" s="42"/>
       <c r="C86" s="6" t="s">
         <v>177</v>
       </c>
@@ -3587,7 +3584,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="35"/>
-      <c r="B87" s="43"/>
+      <c r="B87" s="42"/>
       <c r="C87" s="6" t="s">
         <v>179</v>
       </c>
@@ -3600,7 +3597,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="35"/>
-      <c r="B88" s="43"/>
+      <c r="B88" s="42"/>
       <c r="C88" s="6" t="s">
         <v>182</v>
       </c>
@@ -3613,7 +3610,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="35"/>
-      <c r="B89" s="43"/>
+      <c r="B89" s="42"/>
       <c r="C89" s="6" t="s">
         <v>190</v>
       </c>
@@ -3626,11 +3623,11 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="35"/>
-      <c r="B90" s="43"/>
+      <c r="B90" s="42"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="35"/>
-      <c r="B91" s="46" t="s">
+      <c r="B91" s="45" t="s">
         <v>205</v>
       </c>
       <c r="C91" s="13" t="s">
@@ -3646,7 +3643,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="35"/>
-      <c r="B92" s="43"/>
+      <c r="B92" s="42"/>
       <c r="C92" s="6" t="s">
         <v>203</v>
       </c>
@@ -3659,7 +3656,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="35"/>
-      <c r="B93" s="43"/>
+      <c r="B93" s="42"/>
       <c r="C93" s="6" t="s">
         <v>214</v>
       </c>
@@ -3672,7 +3669,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="35"/>
-      <c r="B94" s="43"/>
+      <c r="B94" s="42"/>
       <c r="C94" s="6" t="s">
         <v>204</v>
       </c>
@@ -3685,7 +3682,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="35"/>
-      <c r="B95" s="43"/>
+      <c r="B95" s="42"/>
       <c r="C95" s="6" t="s">
         <v>216</v>
       </c>
@@ -3698,7 +3695,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="35"/>
-      <c r="B96" s="43"/>
+      <c r="B96" s="42"/>
       <c r="C96" s="6" t="s">
         <v>220</v>
       </c>
@@ -3711,7 +3708,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="35"/>
-      <c r="B97" s="43"/>
+      <c r="B97" s="42"/>
       <c r="C97" s="6" t="s">
         <v>201</v>
       </c>
@@ -3724,7 +3721,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="35"/>
-      <c r="B98" s="43"/>
+      <c r="B98" s="42"/>
       <c r="C98" s="6" t="s">
         <v>275</v>
       </c>
@@ -3737,11 +3734,11 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="35"/>
-      <c r="B99" s="43"/>
+      <c r="B99" s="42"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="35"/>
-      <c r="B100" s="46" t="s">
+      <c r="B100" s="45" t="s">
         <v>221</v>
       </c>
       <c r="C100" s="13" t="s">
@@ -3757,7 +3754,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="35"/>
-      <c r="B101" s="43"/>
+      <c r="B101" s="42"/>
       <c r="C101" s="6" t="s">
         <v>224</v>
       </c>
@@ -3770,7 +3767,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="35"/>
-      <c r="B102" s="43"/>
+      <c r="B102" s="42"/>
       <c r="C102" s="6" t="s">
         <v>232</v>
       </c>
@@ -3783,7 +3780,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="35"/>
-      <c r="B103" s="43"/>
+      <c r="B103" s="42"/>
       <c r="C103" s="6" t="s">
         <v>234</v>
       </c>
@@ -3796,11 +3793,11 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="35"/>
-      <c r="B104" s="43"/>
+      <c r="B104" s="42"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="35"/>
-      <c r="B105" s="46" t="s">
+      <c r="B105" s="45" t="s">
         <v>236</v>
       </c>
       <c r="C105" s="13" t="s">
@@ -3816,7 +3813,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="35"/>
-      <c r="B106" s="43"/>
+      <c r="B106" s="42"/>
       <c r="C106" s="6" t="s">
         <v>239</v>
       </c>
@@ -3829,6 +3826,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B105:B106"/>
     <mergeCell ref="A81:A106"/>
     <mergeCell ref="A2:A22"/>
@@ -3845,11 +3847,6 @@
     <mergeCell ref="B100:B104"/>
     <mergeCell ref="A45:A70"/>
     <mergeCell ref="B51:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="A71:A80"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
